--- a/synthetic_demo_data.xlsx
+++ b/synthetic_demo_data.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -466,12 +466,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Porosity_v6</t>
+          <t>Porosity_WL</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>LogK_Ideal</t>
+          <t>LogK_Core</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -3137,7 +3137,7 @@
         <v>34.05318472225294</v>
       </c>
       <c r="G32" t="n">
-        <v>220.3365939712063</v>
+        <v>220.3365939712062</v>
       </c>
       <c r="H32" t="n">
         <v>0.0941680326383465</v>
@@ -5347,7 +5347,7 @@
         <v>8.514791718323057</v>
       </c>
       <c r="G58" t="n">
-        <v>81.45763514526843</v>
+        <v>81.45763514526841</v>
       </c>
       <c r="H58" t="n">
         <v>0.1785399922347214</v>
@@ -7302,7 +7302,7 @@
         <v>25.88878970572613</v>
       </c>
       <c r="G81" t="n">
-        <v>97.73446610077153</v>
+        <v>97.73446610077151</v>
       </c>
       <c r="H81" t="n">
         <v>0.04976729640732192</v>
@@ -9682,7 +9682,7 @@
         <v>28.32989494487907</v>
       </c>
       <c r="G109" t="n">
-        <v>5.094173203534042</v>
+        <v>5.094173203534043</v>
       </c>
       <c r="H109" t="n">
         <v>0.09871544268017227</v>
@@ -12062,7 +12062,7 @@
         <v>29.64284864213294</v>
       </c>
       <c r="G137" t="n">
-        <v>30.24467806848888</v>
+        <v>30.24467806848887</v>
       </c>
       <c r="H137" t="n">
         <v>0.1182117312579181</v>
@@ -13252,7 +13252,7 @@
         <v>10.71829107209243</v>
       </c>
       <c r="G151" t="n">
-        <v>1912.203686058905</v>
+        <v>1912.203686058904</v>
       </c>
       <c r="H151" t="n">
         <v>0.154185066464257</v>
@@ -16057,7 +16057,7 @@
         <v>27.23768255765382</v>
       </c>
       <c r="G184" t="n">
-        <v>8.857841581251943</v>
+        <v>8.857841581251941</v>
       </c>
       <c r="H184" t="n">
         <v>0.08881491333837954</v>
@@ -17502,7 +17502,7 @@
         <v>26.02953968707644</v>
       </c>
       <c r="G201" t="n">
-        <v>37.08054951658043</v>
+        <v>37.08054951658042</v>
       </c>
       <c r="H201" t="n">
         <v>0.1742804412900914</v>
@@ -17927,7 +17927,7 @@
         <v>5.48733223279392</v>
       </c>
       <c r="G206" t="n">
-        <v>2.737794040891795</v>
+        <v>2.737794040891794</v>
       </c>
       <c r="H206" t="n">
         <v>0.2427248951871734</v>
